--- a/safety_inspection_forms/049_ladder_safety_quiz--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/049_ladder_safety_quiz--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'4_feet'}</t>
+          <t>4_feet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': '4 feet'}</t>
+          <t>4 feet</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'5_feet'}</t>
+          <t>5_feet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '5 feet'}</t>
+          <t>5 feet</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'6_feet'}</t>
+          <t>6_feet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '6 feet'}</t>
+          <t>6 feet</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'do_not_use'}</t>
+          <t>do_not_use</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Do not use'}</t>
+          <t>Do not use</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'inspect_and_repair'}</t>
+          <t>inspect_and_repair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Inspect and repair'}</t>
+          <t>Inspect and repair</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'replace'}</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Replace'}</t>
+          <t>Replace</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'foot_on_the_rung_side'}</t>
+          <t>foot_on_the_rung_side</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Foot on the rung side'}</t>
+          <t>Foot on the rung side</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'foot_on_the_side_of_the_rung'}</t>
+          <t>foot_on_the_side_of_the_rung</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Foot on the side of the rung'}</t>
+          <t>Foot on the side of the rung</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'foot_on_the_center_of_the_rung'}</t>
+          <t>foot_on_the_center_of_the_rung</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Foot on the center of the rung'}</t>
+          <t>Foot on the center of the rung</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'look_down'}</t>
+          <t>look_down</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Look down'}</t>
+          <t>Look down</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'look_up'}</t>
+          <t>look_up</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Look up'}</t>
+          <t>Look up</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'never_look_at_the_top'}</t>
+          <t>never_look_at_the_top</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Never look at the top'}</t>
+          <t>Never look at the top</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'both_hands_on_the_side'}</t>
+          <t>both_hands_on_the_side</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Both hands on the side'}</t>
+          <t>Both hands on the side</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'right_hand_on_the_side_and_left_hand_on_the_top'}</t>
+          <t>right_hand_on_the_side_and_left_hand_on_the_top</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Right hand on the side and left hand on the top'}</t>
+          <t>Right hand on the side and left hand on the top</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'left_hand_on_the_side_and_right_hand_on_top'}</t>
+          <t>left_hand_on_the_side_and_right_hand_on_top</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Left hand on the side and right hand on top'}</t>
+          <t>Left hand on the side and right hand on top</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'foot_over_foot'}</t>
+          <t>foot_over_foot</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Foot over foot'}</t>
+          <t>Foot over foot</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'side_over_side'}</t>
+          <t>side_over_side</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Side over side'}</t>
+          <t>Side over side</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'when_necessary'}</t>
+          <t>when_necessary</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'When necessary'}</t>
+          <t>When necessary</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'before_using'}</t>
+          <t>before_using</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Before using'}</t>
+          <t>Before using</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'1_year'}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': '1 year'}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'2_years'}</t>
+          <t>2_years</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': '2 years'}</t>
+          <t>2 years</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'3_years'}</t>
+          <t>3_years</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': '3 years'}</t>
+          <t>3 years</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'200_lbs'}</t>
+          <t>200_lbs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': '200 lbs'}</t>
+          <t>200 lbs</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'300_lbs'}</t>
+          <t>300_lbs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': '300 lbs'}</t>
+          <t>300 lbs</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'400_lbs'}</t>
+          <t>400_lbs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': '400 lbs'}</t>
+          <t>400 lbs</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'75_degrees'}</t>
+          <t>75_degrees</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': '75 degrees'}</t>
+          <t>75 degrees</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'90_degrees'}</t>
+          <t>90_degrees</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': '90 degrees'}</t>
+          <t>90 degrees</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'120_degrees'}</t>
+          <t>120_degrees</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': '120 degrees'}</t>
+          <t>120 degrees</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'visually'}</t>
+          <t>visually</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Visually'}</t>
+          <t>Visually</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'by_weight'}</t>
+          <t>by_weight</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'By weight'}</t>
+          <t>By weight</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'when_necessary'}</t>
+          <t>when_necessary</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'When necessary'}</t>
+          <t>When necessary</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'replace'}</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'Replace'}</t>
+          <t>Replace</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'repurpose'}</t>
+          <t>repurpose</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'Repurpose'}</t>
+          <t>Repurpose</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_'retire'}</t>
+          <t>retire</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 'Retire'}</t>
+          <t>Retire</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'remove_it_from_service'}</t>
+          <t>remove_it_from_service</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'Remove it from service'}</t>
+          <t>Remove it from service</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'repair_it'}</t>
+          <t>repair_it</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'Repair it'}</t>
+          <t>Repair it</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'return_it_to_service'}</t>
+          <t>return_it_to_service</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'Return it to service'}</t>
+          <t>Return it to service</t>
         </is>
       </c>
     </row>
